--- a/Barwert.xlsx
+++ b/Barwert.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FHAC\Bayernallee\Verwaltung\Kommissionen\DWA\WI 2\bearbeitungen\b260424\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FHAC\Bayernallee\Verwaltung\Kommissionen\DWA\WI 2\bearbeitungen\b260511\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4551DFA7-A5C7-4132-9798-30FB8B4E9EF9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D46F9C-79CA-4D34-A930-C0BF5940BEAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="57600" windowHeight="29700" xr2:uid="{3C469100-3F29-4E6C-AF5C-FA68EBCBD28B}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Zinssatzverlauf" sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="clipboard" localSheetId="0">'Ab 4.7 (3%)'!$A$3:$B$53</definedName>
+    <definedName name="clipboard" localSheetId="0">'Ab 4.7 (3%)'!#REF!</definedName>
     <definedName name="clipboard" localSheetId="1">'Ab 4.7 variabel'!$A$3:$B$53</definedName>
     <definedName name="clipboard" localSheetId="2">'Ab. 5.2'!$A$3:$B$10</definedName>
   </definedNames>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
   <si>
     <t>Jahr</t>
   </si>
@@ -119,12 +119,78 @@
   <si>
     <t>Beispielprojekt gem. DWA-M 816 mit var. Zinssatzverlauf</t>
   </si>
+  <si>
+    <t>Abzinsung</t>
+  </si>
+  <si>
+    <t>Abzinsungsreihe</t>
+  </si>
+  <si>
+    <t>Allgemeine Parameter</t>
+  </si>
+  <si>
+    <t>Pacht</t>
+  </si>
+  <si>
+    <t>Verkauf Altanlage</t>
+  </si>
+  <si>
+    <t>3a</t>
+  </si>
+  <si>
+    <t>3b</t>
+  </si>
+  <si>
+    <t>4a</t>
+  </si>
+  <si>
+    <t>Personalrückgang</t>
+  </si>
+  <si>
+    <t>4b</t>
+  </si>
+  <si>
+    <t>Personalstandard</t>
+  </si>
+  <si>
+    <t>Instandhaltung&amp;Optimierung</t>
+  </si>
+  <si>
+    <t>Kapitaldienst Erstinvest</t>
+  </si>
+  <si>
+    <t>Kapitaldienst Teilreplikation</t>
+  </si>
+  <si>
+    <t>Barwert:</t>
+  </si>
+  <si>
+    <t>Instandhaltung&amp;Optimierung:</t>
+  </si>
+  <si>
+    <t>Pacht:</t>
+  </si>
+  <si>
+    <t>Verkauf Altanlage:</t>
+  </si>
+  <si>
+    <t>Kapitaldienst Erstinvest:</t>
+  </si>
+  <si>
+    <t>Kapitaldienst Teilreplikation:</t>
+  </si>
+  <si>
+    <t>Personalrückgang:</t>
+  </si>
+  <si>
+    <t>Personalstandard:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +252,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -201,7 +275,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -271,13 +345,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -303,13 +395,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -327,6 +433,231 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1095374</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>457199</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>180976</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Sprechblase: rechteckig mit abgerundeten Ecken 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48DF4332-DE31-4903-848A-074DD6133190}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11201399" y="781050"/>
+          <a:ext cx="3724275" cy="1133476"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -66897"/>
+            <a:gd name="adj2" fmla="val -15070"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="107950" dist="12700" dir="5400000" algn="ctr">
+            <a:srgbClr val="000000"/>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="soft" dir="t">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d contourW="44450" prstMaterial="matte">
+          <a:bevelT w="63500" h="63500" prst="artDeco"/>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400"/>
+            <a:t>1. Umrahmten</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" baseline="0"/>
+            <a:t> Bereich kopieren (Strg + c)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" baseline="0"/>
+            <a:t>2. Python-Programm starten</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" baseline="0"/>
+            <a:t>3. Schaltfläche anklicken</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" baseline="0"/>
+            <a:t>     ...</a:t>
+          </a:r>
+          <a:endParaRPr lang="de-DE" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Sprechblase: rechteckig mit abgerundeten Ecken 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E3DFBB5-D034-48E2-B95D-A469270CE03D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6067425" y="3657600"/>
+          <a:ext cx="8877300" cy="885825"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -66897"/>
+            <a:gd name="adj2" fmla="val -15070"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="107950" dist="12700" dir="5400000" algn="ctr">
+            <a:srgbClr val="000000"/>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="soft" dir="t">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d contourW="44450" prstMaterial="matte">
+          <a:bevelT w="63500" h="63500" prst="artDeco"/>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" baseline="0"/>
+            <a:t>     ...</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" baseline="0"/>
+            <a:t>4. Berechnungsergebnis einfügen (Strg + v)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" baseline="0"/>
+            <a:t>5. Ausführliche Berechnung in Datei: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" baseline="0">
+              <a:latin typeface="Lucida Console" panose="020B0609040504020204" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>C:\Users\hoettges\Documents\kvr.txt</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -626,400 +957,387 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF13CB0-2E5A-4486-BE74-600EE477CA3F}">
-  <dimension ref="A1:B53"/>
+  <sheetPr codeName="Tabelle1"/>
+  <dimension ref="B2:K33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="2" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="13"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+    <row r="3" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="23">
+        <v>30</v>
+      </c>
+      <c r="E5" s="24">
+        <v>0.03</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="31"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="17"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="31">
+        <v>1</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="23">
+        <v>2026</v>
+      </c>
+      <c r="E8" s="23">
+        <v>30</v>
+      </c>
+      <c r="F8" s="23">
+        <v>150000</v>
+      </c>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="31">
+        <v>2</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="23">
+        <v>2026</v>
+      </c>
+      <c r="E9" s="23">
+        <v>1</v>
+      </c>
+      <c r="F9" s="23">
+        <v>-1000000</v>
+      </c>
+      <c r="G9" s="23">
+        <v>3</v>
+      </c>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="23">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="23">
+        <v>20</v>
+      </c>
+      <c r="F10" s="23">
+        <v>526400</v>
+      </c>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23">
+        <v>8400</v>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="23">
+        <v>2026</v>
+      </c>
+      <c r="E11" s="23">
+        <v>4</v>
+      </c>
+      <c r="F11" s="23">
+        <v>1212990.3160342509</v>
+      </c>
+      <c r="G11" s="23">
+        <v>25</v>
+      </c>
+      <c r="H11" s="23">
+        <v>23215.12566572729</v>
+      </c>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="23">
+        <v>2026</v>
+      </c>
+      <c r="E12" s="23">
+        <v>10</v>
+      </c>
+      <c r="F12" s="23">
+        <v>400000</v>
+      </c>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23">
+        <v>16000</v>
+      </c>
+      <c r="I12" s="33">
+        <v>0.02</v>
+      </c>
+      <c r="J12" s="23"/>
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="23">
+        <v>2036</v>
+      </c>
+      <c r="E13" s="23">
+        <v>20</v>
+      </c>
+      <c r="F13" s="23">
+        <v>292558.66079874168</v>
+      </c>
+      <c r="G13" s="23">
+        <v>10</v>
+      </c>
+      <c r="H13" s="23"/>
+      <c r="I13" s="33">
+        <v>0.02</v>
+      </c>
+      <c r="J13" s="23"/>
+      <c r="K13" s="16"/>
+    </row>
+    <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="34">
         <v>5</v>
       </c>
-      <c r="B4" s="15">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="16">
+      <c r="C14" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="35">
+        <v>2026</v>
+      </c>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35">
+        <v>300000</v>
+      </c>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35">
+        <v>30000</v>
+      </c>
+      <c r="I14" s="36">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J14" s="35">
+        <v>1500</v>
+      </c>
+      <c r="K14" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="22"/>
+    </row>
+    <row r="19" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="22">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20">
+        <v>2940066.2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="22">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21">
+        <v>-888487.05</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22">
+        <v>6641423.2400000002</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="22" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="16"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="16">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="16">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="16">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="16"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="16"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="16">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="16">
-        <v>-1000000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="16"/>
-    </row>
-    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="20"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="16">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" s="16">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="16">
-        <f>526400-B23*0</f>
-        <v>526400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="16">
-        <v>8400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="16"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="20"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="16">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="16">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="16">
-        <f>(836000-16000*0)*1.015^25</f>
-        <v>1212990.3160342509</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="16">
-        <f>16000*1.015^25</f>
-        <v>23215.12566572729</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="16"/>
-    </row>
-    <row r="32" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" s="20"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="16">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" s="16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="16">
-        <f>(400000-B36*0)*(1+B37)^0</f>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="16">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="21">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="21"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" s="20"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="16">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B42" s="16">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="16">
-        <f>240000*1.02^(10+0)</f>
-        <v>292558.66079874168</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="21">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="21"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B46" s="20"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="19"/>
-      <c r="B47" s="20"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="16">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B49" s="16">
-        <f>(300000-0*B50+0^2*B51)*(1+B52)^0</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="16">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B51" s="16">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B52" s="21">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="23">
-        <v>2</v>
-      </c>
-    </row>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23">
+        <v>2051917.56</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24">
+        <v>2970365.76</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25">
+        <v>3936123.06</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="22">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26">
+        <v>3551986.9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28">
+        <v>21203395.68</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A46:B47"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A4:A5 A8:A10 A13:A16 A20:A23 A26:A30 A33:A37 A40:A44 A48:A53" xr:uid="{3403308F-A94D-4C0B-89D8-41B0ECAACFAB}">
-      <formula1>"Gesamtlaufzeit,Inflation,Jahr,Einmalzahlung,1. Rate,Laufzeit,Vorlaufzeit,Abnahme pro Jahr,Zunahme pro Jahr,Zahltakt,Quadratische Steigerung,Steigerungsrate"</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:E4" xr:uid="{398239C6-37F6-49C0-A7C8-7DCB9882B2AA}">
+      <formula1>"Gesamtlaufzeit,Abzinsung,Abzinsungsreihe,Jahr,Einmalzahlung,1. Rate,Laufzeit,Vorlaufzeit,Abnahme pro Jahr,Zunahme pro Jahr,Zahltakt,Quadratische Steigerung,Steigerungsrate"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fehler" error="Bitte wählen Sie aus der Liste" promptTitle="Parameterauswahl" prompt="Bitte wählen Sie aus der Liste" sqref="D7:K7" xr:uid="{E657CB80-E10A-44CE-A13B-65EB3AF6982D}">
+      <formula1>"Gesamtlaufzeit,Abzinsung,Abzinsungsreihe,Jahr,Einmalzahlung,1. Rate,Laufzeit,Vorlaufzeit,Abnahme pro Jahr,Zunahme pro Jahr,Zahltakt,Quadratische Steigerung,Steigerungsrate"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE77A69F-8A03-4789-9ED6-E6200DFD5EE2}">
+  <sheetPr codeName="Tabelle2"/>
   <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1040,7 +1358,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B4" s="15" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,Zinssatzverlauf!A6:A55)</f>
@@ -1136,14 +1454,14 @@
       <c r="B17" s="16"/>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="20"/>
+      <c r="B18" s="27"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
@@ -1183,10 +1501,10 @@
       <c r="B24" s="16"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="20"/>
+      <c r="B25" s="27"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
@@ -1235,10 +1553,10 @@
       <c r="B31" s="16"/>
     </row>
     <row r="32" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="20"/>
+      <c r="B32" s="27"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
@@ -1277,19 +1595,19 @@
       <c r="A37" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="19">
         <v>0.02</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
-      <c r="B38" s="21"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="27"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
@@ -1328,23 +1646,23 @@
       <c r="A44" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="21">
+      <c r="B44" s="19">
         <v>0.02</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
-      <c r="B45" s="21"/>
+      <c r="B45" s="19"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="20"/>
+      <c r="B46" s="27"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="19"/>
-      <c r="B47" s="20"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="27"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
@@ -1383,15 +1701,15 @@
       <c r="A52" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="19">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B53" s="21">
         <v>2</v>
       </c>
     </row>
@@ -1403,9 +1721,12 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A46:B47"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A4:A5 A8:A10 A13:A16 A20:A23 A26:A30 A33:A37 A40:A44 A48:A53" xr:uid="{FF103844-55B3-4057-9B81-7361C7E923DA}">
-      <formula1>"Gesamtlaufzeit,Inflation,Jahr,Einmalzahlung,1. Rate,Laufzeit,Vorlaufzeit,Abnahme pro Jahr,Zunahme pro Jahr,Zahltakt,Quadratische Steigerung,Steigerungsrate"</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fehler" error="Bitte wählen Sie aus der Liste" promptTitle="Parameterauswahl" prompt="Bitte wählen Sie aus der Liste" sqref="A48:A53 A40:A44 A33:A37 A26:A30 A20:A23 A13:A16 A8:A10" xr:uid="{3A5785BD-EE3B-402A-AF1A-01BBC27AA531}">
+      <formula1>"Gesamtlaufzeit,Abzinsung,Abzinsungsreihe,Jahr,Einmalzahlung,1. Rate,Laufzeit,Vorlaufzeit,Abnahme pro Jahr,Zunahme pro Jahr,Zahltakt,Quadratische Steigerung,Steigerungsrate"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A4:A5" xr:uid="{F7181187-18FA-4F0A-9338-14BB3E0B8B65}">
+      <formula1>"Gesamtlaufzeit,Abzinsung,Abzinsungsreihe,Jahr,Einmalzahlung,1. Rate,Laufzeit,Vorlaufzeit,Abnahme pro Jahr,Zunahme pro Jahr,Zahltakt,Quadratische Steigerung,Steigerungsrate"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1415,6 +1736,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF6A6446-2012-4DDF-A8D9-D1F15845DEB6}">
+  <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1476,10 +1798,10 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="21">
         <f>486400/B9</f>
         <v>32426.666666666668</v>
       </c>
@@ -1487,9 +1809,12 @@
     <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A4:A5 A8:A10" xr:uid="{1669814E-CBAC-4B89-91DC-F8BCCE407609}">
-      <formula1>"Gesamtlaufzeit,Inflation,Jahr,Einmalzahlung,1. Rate,Laufzeit,Vorlaufzeit,Abnahme pro Jahr,Zunahme pro Jahr,Zahltakt,Quadratische Steigerung,Steigerungsrate"</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fehler" error="Bitte wählen Sie aus der Liste" promptTitle="Parameterauswahl" prompt="Bitte wählen Sie aus der Liste" sqref="A8:A10" xr:uid="{BD3B5A6C-BC16-4F0C-BB41-96CEB7844AA3}">
+      <formula1>"Gesamtlaufzeit,Abzinsung,Abzinsungsreihe,Jahr,Einmalzahlung,1. Rate,Laufzeit,Vorlaufzeit,Abnahme pro Jahr,Zunahme pro Jahr,Zahltakt,Quadratische Steigerung,Steigerungsrate"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A4:A5" xr:uid="{F36D9E1B-2EF8-445C-94A3-6AAC39582091}">
+      <formula1>"Gesamtlaufzeit,Abzinsung,Abzinsungsreihe,Jahr,Einmalzahlung,1. Rate,Laufzeit,Vorlaufzeit,Abnahme pro Jahr,Zunahme pro Jahr,Zahltakt,Quadratische Steigerung,Steigerungsrate"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1499,6 +1824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B024D5D1-D11D-4A88-83B6-5F0230F62FF4}">
+  <sheetPr codeName="Tabelle4"/>
   <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/Barwert.xlsx
+++ b/Barwert.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FHAC\Bayernallee\Verwaltung\Kommissionen\DWA\WI 2\bearbeitungen\b260511\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D46F9C-79CA-4D34-A930-C0BF5940BEAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCB312A-59D3-47B6-9146-4B51597921D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="57600" windowHeight="29700" xr2:uid="{3C469100-3F29-4E6C-AF5C-FA68EBCBD28B}"/>
   </bookViews>
@@ -402,10 +402,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -416,6 +412,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -650,7 +650,7 @@
             <a:rPr lang="de-DE" sz="1400" baseline="0">
               <a:latin typeface="Lucida Console" panose="020B0609040504020204" pitchFamily="49" charset="0"/>
             </a:rPr>
-            <a:t>C:\Users\hoettges\Documents\kvr.txt</a:t>
+            <a:t>Dokumente\kvr.txt</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -976,25 +976,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="28"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="30" t="s">
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
       <c r="K4" s="13"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       <c r="K5" s="16"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="31"/>
+      <c r="B6" s="29"/>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
       <c r="E6" s="23"/>
@@ -1050,12 +1050,12 @@
       <c r="J7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="31">
+      <c r="B8" s="29">
         <v>1</v>
       </c>
       <c r="C8" s="23" t="s">
@@ -1077,7 +1077,7 @@
       <c r="K8" s="16"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="31">
+      <c r="B9" s="29">
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -1101,7 +1101,7 @@
       <c r="K9" s="16"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="29" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="23" t="s">
@@ -1125,7 +1125,7 @@
       <c r="K10" s="16"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="29" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="23" t="s">
@@ -1151,7 +1151,7 @@
       <c r="K11" s="16"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="29" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="23" t="s">
@@ -1170,14 +1170,14 @@
       <c r="H12" s="23">
         <v>16000</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="31">
         <v>0.02</v>
       </c>
       <c r="J12" s="23"/>
       <c r="K12" s="16"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="29" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="23" t="s">
@@ -1196,34 +1196,34 @@
         <v>10</v>
       </c>
       <c r="H13" s="23"/>
-      <c r="I13" s="33">
+      <c r="I13" s="31">
         <v>0.02</v>
       </c>
       <c r="J13" s="23"/>
       <c r="K13" s="16"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="34">
+      <c r="B14" s="32">
         <v>5</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="33">
         <v>2026</v>
       </c>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35">
+      <c r="E14" s="33"/>
+      <c r="F14" s="33">
         <v>300000</v>
       </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35">
+      <c r="G14" s="33"/>
+      <c r="H14" s="33">
         <v>30000</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="34">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="33">
         <v>1500</v>
       </c>
       <c r="K14" s="21">
@@ -1454,14 +1454,14 @@
       <c r="B17" s="16"/>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="27"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
@@ -1501,10 +1501,10 @@
       <c r="B24" s="16"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="27"/>
+      <c r="B25" s="37"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
@@ -1553,10 +1553,10 @@
       <c r="B31" s="16"/>
     </row>
     <row r="32" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="27"/>
+      <c r="B32" s="37"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
@@ -1604,10 +1604,10 @@
       <c r="B38" s="19"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B39" s="27"/>
+      <c r="B39" s="37"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
@@ -1655,14 +1655,14 @@
       <c r="B45" s="19"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="27"/>
+      <c r="B46" s="37"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="26"/>
-      <c r="B47" s="27"/>
+      <c r="A47" s="36"/>
+      <c r="B47" s="37"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
